--- a/docs/Planner_Import_Workbook_CHECKPOINT.xlsx
+++ b/docs/Planner_Import_Workbook_CHECKPOINT.xlsx
@@ -520,14 +520,14 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Sprints 0, 1 and 2 are COMPLETE. Their tasks are recorded here with a Status of Done and are evidenced by the repository history and the passing test suite.</t>
+          <t>Sprints 0, 1, 2 and 3 are COMPLETE. Their tasks are recorded here with a Status of Done and are evidenced by the repository history and the passing test suite.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Sprints 3, 4, 5 and Finalization are still to do, and run from September 4 to the September 23 deadline.</t>
+          <t>Sprints 0, 1, 2 and 3 are COMPLETE. Sprint 3 is evidenced by the repository history and the passing test suite (182 server tests, 18 client tests). Sprints 4, 5 and Finalization run to the September 23 deadline.</t>
         </is>
       </c>
     </row>
@@ -3484,12 +3484,13 @@
       </c>
       <c r="P31" s="5" t="inlineStr">
         <is>
-          <t>A week of trips can be created from one schedule, and a single day can still be overridden.</t>
+          <t>A week of trips can be created from one schedule, and a single day can still be overridden.
+Done. Schedule model + scheduleService.js generate a rolling 7-day window; unique (schedule, service day) index prevents duplicates; one day can be cancelled, deleted or edited without breaking the pattern. Admin Trips page.</t>
         </is>
       </c>
       <c r="Q31" s="7" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -3574,12 +3575,13 @@
       </c>
       <c r="P32" s="5" t="inlineStr">
         <is>
-          <t>A wrong checkpoint logged an hour ago can be fixed without touching the database directly.</t>
+          <t>A wrong checkpoint logged an hour ago can be fixed without touching the database directly.
+Done. Admin trip page shows the full log stream; add, correct or remove an update, each replaying the trip and writing a TripCorrection audit record.</t>
         </is>
       </c>
       <c r="Q32" s="7" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -3665,12 +3667,13 @@
       </c>
       <c r="P33" s="5" t="inlineStr">
         <is>
-          <t>A leg measured off-peak no longer causes every peak trip to read as late.</t>
+          <t>A leg measured off-peak no longer causes every peak trip to read as late.
+Done. Routes carry per-band figures (MMDA rush hours); a trip picks each leg’s band from when it is due to drive it, with the single-value fallback intact.</t>
         </is>
       </c>
       <c r="Q33" s="7" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -3755,12 +3758,13 @@
       </c>
       <c r="P34" s="5" t="inlineStr">
         <is>
-          <t>The conductor app opens and accepts taps with no connection at all.</t>
+          <t>The conductor app opens and accepts taps with no connection at all.
+Done. Service worker caches the app shell; staff screens keep their last answer per account; a network failure no longer signs anyone out.</t>
         </is>
       </c>
       <c r="Q34" s="7" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -3845,12 +3849,13 @@
       </c>
       <c r="P35" s="5" t="inlineStr">
         <is>
-          <t>Repeated failed sign-ins are throttled and a conductor can recover their own password.</t>
+          <t>Repeated failed sign-ins are throttled and a conductor can recover their own password.
+Done. Sign-in throttling per account and address, temporary passwords on admin-created accounts, one-time reset codes, sessions ended on password change.</t>
         </is>
       </c>
       <c r="Q35" s="7" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -3935,12 +3940,13 @@
       </c>
       <c r="P36" s="5" t="inlineStr">
         <is>
-          <t>Every Sprint 3 story is covered and the suite passes.</t>
+          <t>Every Sprint 3 story is covered and the suite passes.
+Done. 182 server tests and 18 client tests pass, covering schedule generation and duplicate protection, corrections and the audit trail, and band selection.</t>
         </is>
       </c>
       <c r="Q36" s="7" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
